--- a/AAII_Financials/Quarterly/FRFC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRFC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>FRFC</t>
   </si>
@@ -656,92 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>40999</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>40908</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>40633</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>40543</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F8" s="3">
         <v>4100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2100</v>
       </c>
       <c r="K8" s="3">
         <v>2100</v>
@@ -750,10 +757,16 @@
         <v>2100</v>
       </c>
       <c r="M8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O8" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +800,14 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +841,14 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +862,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +899,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +940,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -942,8 +981,14 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1022,14 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,78 +1040,92 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="E18" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="F18" s="3">
         <v>2500</v>
       </c>
       <c r="G18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I18" s="3">
         <v>2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,43 +1139,51 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1900</v>
+        <v>-1800</v>
       </c>
       <c r="E20" s="3">
         <v>-1700</v>
       </c>
       <c r="F20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1129,23 +1202,29 @@
       <c r="H21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="3">
         <v>800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,43 +1258,55 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>700</v>
+      </c>
+      <c r="F23" s="3">
         <v>600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1226,13 +1317,13 @@
         <v>200</v>
       </c>
       <c r="F24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>200</v>
       </c>
       <c r="H24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I24" s="3">
         <v>200</v>
@@ -1241,16 +1332,22 @@
         <v>300</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L24" s="3">
         <v>300</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>300</v>
+      </c>
+      <c r="O24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,8 +1381,14 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1293,34 +1396,40 @@
         <v>400</v>
       </c>
       <c r="E26" s="3">
+        <v>500</v>
+      </c>
+      <c r="F26" s="3">
+        <v>400</v>
+      </c>
+      <c r="G26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1328,34 +1437,40 @@
         <v>400</v>
       </c>
       <c r="E27" s="3">
+        <v>500</v>
+      </c>
+      <c r="F27" s="3">
+        <v>400</v>
+      </c>
+      <c r="G27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1504,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1545,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1586,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,43 +1627,55 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E32" s="3">
         <v>1700</v>
       </c>
       <c r="F32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1538,34 +1683,40 @@
         <v>400</v>
       </c>
       <c r="E33" s="3">
+        <v>500</v>
+      </c>
+      <c r="F33" s="3">
+        <v>400</v>
+      </c>
+      <c r="G33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,8 +1750,14 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1608,74 +1765,86 @@
         <v>400</v>
       </c>
       <c r="E35" s="3">
+        <v>500</v>
+      </c>
+      <c r="F35" s="3">
+        <v>400</v>
+      </c>
+      <c r="G35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>40999</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>40908</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>40633</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>40543</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1858,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,32 +1875,34 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F41" s="3">
         <v>12700</v>
-      </c>
-      <c r="E41" s="3">
-        <v>18400</v>
-      </c>
-      <c r="F41" s="3">
-        <v>29200</v>
       </c>
       <c r="G41" s="3">
         <v>18400</v>
       </c>
       <c r="H41" s="3">
+        <v>29200</v>
+      </c>
+      <c r="I41" s="3">
+        <v>18400</v>
+      </c>
+      <c r="J41" s="3">
         <v>12900</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1739,32 +1912,38 @@
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F42" s="3">
         <v>6100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>13300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>15000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>4600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>16900</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
       </c>
@@ -1774,8 +1953,14 @@
       <c r="M42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1809,8 +1994,14 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1844,8 +2035,14 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1879,8 +2076,14 @@
       <c r="M45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1914,8 +2117,14 @@
       <c r="M46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1949,8 +2158,14 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1958,23 +2173,23 @@
         <v>6100</v>
       </c>
       <c r="E48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F48" s="3">
         <v>6100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H48" s="3">
         <v>6200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6400</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
@@ -1984,8 +2199,14 @@
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2019,8 +2240,14 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2281,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,32 +2322,38 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5600</v>
+        <v>4600</v>
       </c>
       <c r="E52" s="3">
-        <v>5200</v>
+        <v>5800</v>
       </c>
       <c r="F52" s="3">
         <v>5600</v>
       </c>
       <c r="G52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I52" s="3">
         <v>5900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>5000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2124,8 +2363,14 @@
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,32 +2404,38 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>484300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>464000</v>
+      </c>
+      <c r="F54" s="3">
         <v>462300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>472000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>485800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>456500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>457200</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2194,8 +2445,14 @@
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2466,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,32 +2483,34 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2259,8 +2520,14 @@
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2294,8 +2561,14 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2329,8 +2602,14 @@
       <c r="M59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2364,32 +2643,38 @@
       <c r="M60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F61" s="3">
         <v>2300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2399,8 +2684,14 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2434,8 +2725,14 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2766,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2807,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,32 +2848,38 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>459000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>442000</v>
+      </c>
+      <c r="F66" s="3">
         <v>440000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>449200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>464300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>436100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>435200</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2574,8 +2889,14 @@
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2910,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2947,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2988,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +3029,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,32 +3070,38 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>32100</v>
+      </c>
+      <c r="F72" s="3">
         <v>31800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>31500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>31100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>30700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>30200</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
@@ -2764,8 +3111,14 @@
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +3152,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3193,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,32 +3234,38 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F76" s="3">
         <v>22200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>22800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>21500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>20400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>22000</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
@@ -2904,8 +3275,14 @@
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,48 +3316,60 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>40999</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>40908</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>40633</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>40543</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2988,34 +3377,40 @@
         <v>400</v>
       </c>
       <c r="E81" s="3">
+        <v>500</v>
+      </c>
+      <c r="F81" s="3">
+        <v>400</v>
+      </c>
+      <c r="G81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,8 +3424,10 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3064,8 +3461,14 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3502,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3543,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3584,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3625,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,8 +3666,14 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3274,8 +3707,14 @@
       <c r="M89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,8 +3728,10 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3322,10 +3763,16 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3806,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,8 +3847,14 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3429,8 +3888,14 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3909,10 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3479,8 +3946,14 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3987,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +4028,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,8 +4069,14 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3619,8 +4110,14 @@
       <c r="M100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3654,8 +4151,14 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3687,6 +4190,12 @@
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FRFC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRFC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>FRFC</t>
   </si>
@@ -656,105 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>40999</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>40908</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>40633</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>40543</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F8" s="3">
         <v>4800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3100</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2100</v>
-      </c>
-      <c r="L8" s="3">
-        <v>2100</v>
       </c>
       <c r="M8" s="3">
         <v>2100</v>
@@ -763,10 +771,16 @@
         <v>2100</v>
       </c>
       <c r="O8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q8" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +820,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +867,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +890,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +933,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +980,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1027,14 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1074,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1094,104 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F18" s="3">
         <v>2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>2400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>2500</v>
       </c>
       <c r="H18" s="3">
         <v>2500</v>
       </c>
       <c r="I18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K18" s="3">
         <v>2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1207,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1150,40 +1218,46 @@
         <v>-1800</v>
       </c>
       <c r="E20" s="3">
-        <v>-1700</v>
+        <v>-2000</v>
       </c>
       <c r="F20" s="3">
-        <v>-1900</v>
+        <v>-1800</v>
       </c>
       <c r="G20" s="3">
         <v>-1700</v>
       </c>
       <c r="H20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1208,23 +1282,29 @@
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,54 +1344,66 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>800</v>
+      </c>
+      <c r="F23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E24" s="3">
         <v>200</v>
@@ -1323,13 +1415,13 @@
         <v>200</v>
       </c>
       <c r="H24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>200</v>
       </c>
       <c r="J24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
@@ -1338,16 +1430,22 @@
         <v>300</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N24" s="3">
         <v>300</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1485,108 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="E26" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F26" s="3">
         <v>400</v>
       </c>
       <c r="G26" s="3">
+        <v>500</v>
+      </c>
+      <c r="H26" s="3">
+        <v>400</v>
+      </c>
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="E27" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F27" s="3">
         <v>400</v>
       </c>
       <c r="G27" s="3">
+        <v>500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>400</v>
+      </c>
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1626,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1673,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1720,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1767,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1642,81 +1782,93 @@
         <v>1800</v>
       </c>
       <c r="E32" s="3">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="F32" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="G32" s="3">
         <v>1700</v>
       </c>
       <c r="H32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="E33" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F33" s="3">
         <v>400</v>
       </c>
       <c r="G33" s="3">
+        <v>500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>400</v>
+      </c>
+      <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1908,113 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="E35" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F35" s="3">
         <v>400</v>
       </c>
       <c r="G35" s="3">
+        <v>500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>400</v>
+      </c>
+      <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>40999</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>40908</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>40633</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>40543</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +2030,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,38 +2049,40 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F41" s="3">
         <v>11500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>12800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12700</v>
-      </c>
-      <c r="G41" s="3">
-        <v>18400</v>
-      </c>
-      <c r="H41" s="3">
-        <v>29200</v>
       </c>
       <c r="I41" s="3">
         <v>18400</v>
       </c>
       <c r="J41" s="3">
+        <v>29200</v>
+      </c>
+      <c r="K41" s="3">
+        <v>18400</v>
+      </c>
+      <c r="L41" s="3">
         <v>12900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1918,38 +2092,44 @@
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F42" s="3">
         <v>27900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>10000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>6100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>13300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>15000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>4600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>16900</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>4</v>
       </c>
@@ -1959,8 +2139,14 @@
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2000,8 +2186,14 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2041,8 +2233,14 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2082,8 +2280,14 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2123,8 +2327,14 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2164,8 +2374,14 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2179,23 +2395,23 @@
         <v>6100</v>
       </c>
       <c r="G48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H48" s="3">
         <v>6100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="J48" s="3">
         <v>6200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>6300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>6400</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2205,8 +2421,14 @@
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2246,8 +2468,14 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2515,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,38 +2562,44 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F52" s="3">
         <v>4600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>5800</v>
-      </c>
-      <c r="F52" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>5200</v>
       </c>
       <c r="H52" s="3">
         <v>5600</v>
       </c>
       <c r="I52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K52" s="3">
         <v>5900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>5000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2369,8 +2609,14 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,38 +2656,44 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>460500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>468800</v>
+      </c>
+      <c r="F54" s="3">
         <v>484300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>464000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>462300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>472000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>485800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>456500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>457200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2451,8 +2703,14 @@
       <c r="O54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2726,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,38 +2745,40 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>1900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2526,8 +2788,14 @@
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2567,8 +2835,14 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2608,8 +2882,14 @@
       <c r="O59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2649,38 +2929,44 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F61" s="3">
         <v>2000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2690,8 +2976,14 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2731,8 +3023,14 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +3070,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +3117,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,38 +3164,44 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>433200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>443200</v>
+      </c>
+      <c r="F66" s="3">
         <v>459000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>442000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>440000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>449200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>464300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>436100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>435200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2895,8 +3211,14 @@
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3234,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3277,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3324,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3371,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,38 +3418,44 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>32700</v>
+      </c>
+      <c r="F72" s="3">
         <v>32300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>32100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>31800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>31500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>31100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>30700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>30200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3117,8 +3465,14 @@
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3512,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3559,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,38 +3606,44 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F76" s="3">
         <v>25300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>22000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>22200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>22800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>21500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>22000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3281,8 +3653,14 @@
       <c r="O76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3700,113 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>40999</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>40908</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>40633</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>40543</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="E81" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F81" s="3">
         <v>400</v>
       </c>
       <c r="G81" s="3">
+        <v>500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>400</v>
+      </c>
+      <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,8 +3822,10 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3467,8 +3865,14 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3912,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3959,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +4006,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +4053,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,8 +4100,14 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3713,8 +4147,14 @@
       <c r="O89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +4170,10 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3751,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -3769,10 +4211,16 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4260,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,8 +4307,14 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3894,8 +4354,14 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4377,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3952,8 +4420,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4467,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4514,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,8 +4561,14 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4116,8 +4608,14 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4157,8 +4655,14 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4196,6 +4700,12 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FRFC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRFC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
   <si>
     <t>FRFC</t>
   </si>
@@ -656,116 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>40999</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>40908</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40633</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40543</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5000</v>
+        <v>3800</v>
       </c>
       <c r="E8" s="3">
-        <v>4900</v>
+        <v>4000</v>
       </c>
       <c r="F8" s="3">
-        <v>4800</v>
+        <v>3600</v>
       </c>
       <c r="G8" s="3">
-        <v>4400</v>
+        <v>3100</v>
       </c>
       <c r="H8" s="3">
-        <v>4100</v>
+        <v>3200</v>
       </c>
       <c r="I8" s="3">
-        <v>3800</v>
+        <v>3200</v>
       </c>
       <c r="J8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K8" s="3">
         <v>3700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2100</v>
       </c>
       <c r="N8" s="3">
         <v>2100</v>
@@ -777,10 +781,13 @@
         <v>2100</v>
       </c>
       <c r="Q8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R8" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,31 +833,34 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,31 +1003,34 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1033,31 +1053,34 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1800</v>
+        <v>2800</v>
       </c>
       <c r="E17" s="3">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="F17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H17" s="3">
         <v>2400</v>
       </c>
-      <c r="G17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1600</v>
-      </c>
       <c r="I17" s="3">
-        <v>1300</v>
+        <v>2600</v>
       </c>
       <c r="J17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K17" s="3">
         <v>1200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>400</v>
-      </c>
-      <c r="M17" s="3">
-        <v>500</v>
       </c>
       <c r="N17" s="3">
         <v>500</v>
       </c>
       <c r="O17" s="3">
+        <v>500</v>
+      </c>
+      <c r="P17" s="3">
         <v>1100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3200</v>
+        <v>1000</v>
       </c>
       <c r="E18" s="3">
-        <v>2700</v>
+        <v>1500</v>
       </c>
       <c r="F18" s="3">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="G18" s="3">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="H18" s="3">
+        <v>800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>700</v>
+      </c>
+      <c r="J18" s="3">
+        <v>700</v>
+      </c>
+      <c r="K18" s="3">
         <v>2500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>2700</v>
       </c>
       <c r="L18" s="3">
         <v>2700</v>
       </c>
       <c r="M18" s="3">
-        <v>1600</v>
+        <v>2700</v>
       </c>
       <c r="N18" s="3">
         <v>1600</v>
       </c>
       <c r="O18" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P18" s="3">
         <v>1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,78 +1242,82 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1800</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>-2000</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>-1800</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>-1700</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>-1900</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>-1700</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>-1800</v>
+        <v>-100</v>
       </c>
       <c r="K20" s="3">
         <v>-1800</v>
       </c>
       <c r="L20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F21" s="3">
+        <v>900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1288,46 +1325,49 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1350,75 +1390,81 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>900</v>
+      </c>
+      <c r="E23" s="3">
         <v>1500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
       </c>
       <c r="J24" s="3">
         <v>200</v>
@@ -1427,25 +1473,28 @@
         <v>200</v>
       </c>
       <c r="L24" s="3">
+        <v>200</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>600</v>
       </c>
       <c r="J26" s="3">
         <v>600</v>
       </c>
       <c r="K26" s="3">
+        <v>600</v>
+      </c>
+      <c r="L26" s="3">
         <v>700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>400</v>
-      </c>
-      <c r="I27" s="3">
-        <v>600</v>
       </c>
       <c r="J27" s="3">
         <v>600</v>
       </c>
       <c r="K27" s="3">
+        <v>600</v>
+      </c>
+      <c r="L27" s="3">
         <v>700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1840,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1800</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>2000</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>1800</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>1700</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>1900</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>1700</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3">
         <v>1800</v>
       </c>
       <c r="L32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M32" s="3">
         <v>1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>400</v>
-      </c>
-      <c r="I33" s="3">
-        <v>600</v>
       </c>
       <c r="J33" s="3">
         <v>600</v>
       </c>
       <c r="K33" s="3">
+        <v>600</v>
+      </c>
+      <c r="L33" s="3">
         <v>700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>400</v>
-      </c>
-      <c r="I35" s="3">
-        <v>600</v>
       </c>
       <c r="J35" s="3">
         <v>600</v>
       </c>
       <c r="K35" s="3">
+        <v>600</v>
+      </c>
+      <c r="L35" s="3">
         <v>700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>40999</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>40908</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40633</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40543</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,41 +2137,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13400</v>
+        <v>62500</v>
       </c>
       <c r="E41" s="3">
-        <v>16700</v>
+        <v>22000</v>
       </c>
       <c r="F41" s="3">
-        <v>11500</v>
+        <v>22700</v>
       </c>
       <c r="G41" s="3">
-        <v>12800</v>
+        <v>38400</v>
       </c>
       <c r="H41" s="3">
-        <v>12700</v>
+        <v>21700</v>
       </c>
       <c r="I41" s="3">
+        <v>17800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>30700</v>
+      </c>
+      <c r="K41" s="3">
+        <v>29200</v>
+      </c>
+      <c r="L41" s="3">
         <v>18400</v>
       </c>
-      <c r="J41" s="3">
-        <v>29200</v>
-      </c>
-      <c r="K41" s="3">
-        <v>18400</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12900</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2098,41 +2185,44 @@
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>9800</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>7100</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>27900</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>13300</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>15000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>16900</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2145,31 +2235,34 @@
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2192,31 +2285,34 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2239,31 +2335,34 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2286,31 +2385,34 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>25600</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>26300</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>24700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>20600</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>33200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2333,31 +2435,34 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>169100</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>166600</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>171900</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>174800</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>178900</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>181800</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>185300</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2380,8 +2485,11 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2389,32 +2497,32 @@
         <v>6100</v>
       </c>
       <c r="E48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F48" s="3">
         <v>6200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6100</v>
       </c>
       <c r="I48" s="3">
         <v>6100</v>
       </c>
       <c r="J48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K48" s="3">
         <v>6200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6400</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2427,8 +2535,11 @@
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2439,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G49" s="3">
         <v>0</v>
@@ -2451,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,41 +2685,44 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4100</v>
+        <v>9100</v>
       </c>
       <c r="E52" s="3">
-        <v>4500</v>
+        <v>9000</v>
       </c>
       <c r="F52" s="3">
-        <v>4600</v>
+        <v>7200</v>
       </c>
       <c r="G52" s="3">
-        <v>5800</v>
+        <v>8900</v>
       </c>
       <c r="H52" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K52" s="3">
         <v>5600</v>
       </c>
-      <c r="I52" s="3">
-        <v>5200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>5600</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,41 +2785,44 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>492100</v>
+      </c>
+      <c r="E54" s="3">
         <v>460500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>468800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>484300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>464000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>462300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>472000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>485800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>456500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>457200</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2709,8 +2835,11 @@
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,40 +2877,41 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>700</v>
+        <v>398600</v>
       </c>
       <c r="E57" s="3">
-        <v>700</v>
+        <v>377200</v>
       </c>
       <c r="F57" s="3">
-        <v>1900</v>
+        <v>384200</v>
       </c>
       <c r="G57" s="3">
-        <v>1600</v>
+        <v>362800</v>
       </c>
       <c r="H57" s="3">
-        <v>900</v>
+        <v>350800</v>
       </c>
       <c r="I57" s="3">
-        <v>500</v>
+        <v>359700</v>
       </c>
       <c r="J57" s="3">
+        <v>369900</v>
+      </c>
+      <c r="K57" s="3">
         <v>300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>200</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
+      <c r="M57" s="3">
+        <v>200</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
@@ -2794,31 +2925,34 @@
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>49800</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>53100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>72200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2841,31 +2975,34 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -2888,31 +3025,34 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>456300</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>427700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>438000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>366600</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>436500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>362800</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>442600</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2935,41 +3075,44 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1700</v>
       </c>
-      <c r="E61" s="3">
-        <v>1900</v>
-      </c>
       <c r="F61" s="3">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="G61" s="3">
+        <v>88800</v>
+      </c>
+      <c r="H61" s="3">
         <v>2200</v>
       </c>
-      <c r="H61" s="3">
-        <v>2300</v>
-      </c>
       <c r="I61" s="3">
-        <v>2400</v>
+        <v>73600</v>
       </c>
       <c r="J61" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K61" s="3">
         <v>2600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2982,31 +3125,34 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,41 +3325,44 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>461300</v>
+      </c>
+      <c r="E66" s="3">
         <v>433200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>443200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>459000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>442000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>440000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>449200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>464300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>436100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>435200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3217,8 +3375,11 @@
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,41 +3595,44 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E72" s="3">
         <v>33700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>32700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>32300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>32100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>31800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>31500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>31100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30200</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3471,8 +3645,11 @@
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,41 +3795,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E76" s="3">
         <v>27300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3659,8 +3845,11 @@
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>40999</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>40908</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40633</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40543</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>400</v>
-      </c>
-      <c r="I81" s="3">
-        <v>600</v>
       </c>
       <c r="J81" s="3">
         <v>600</v>
       </c>
       <c r="K81" s="3">
+        <v>600</v>
+      </c>
+      <c r="L81" s="3">
         <v>700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,31 +4022,32 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3871,8 +4070,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,31 +4320,34 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -4153,8 +4370,11 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4392,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,31 +4540,34 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -4360,8 +4590,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,31 +4612,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,31 +4810,34 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -4614,31 +4860,34 @@
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4661,31 +4910,34 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -4706,6 +4958,9 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FRFC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRFC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>FRFC</t>
   </si>
@@ -656,123 +656,126 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>40999</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40633</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40543</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3200</v>
       </c>
       <c r="I8" s="3">
         <v>3200</v>
       </c>
       <c r="J8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K8" s="3">
         <v>3100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3100</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2100</v>
       </c>
       <c r="O8" s="3">
         <v>2100</v>
@@ -784,10 +787,13 @@
         <v>2100</v>
       </c>
       <c r="R8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S8" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -836,35 +842,38 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3100</v>
-      </c>
-      <c r="H10" s="3">
-        <v>3200</v>
       </c>
       <c r="I10" s="3">
         <v>3200</v>
       </c>
       <c r="J10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K10" s="3">
         <v>3100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -886,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1032,8 +1051,8 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1056,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1083,7 +1105,7 @@
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1106,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
-      </c>
-      <c r="N17" s="3">
-        <v>500</v>
       </c>
       <c r="O17" s="3">
         <v>500</v>
       </c>
       <c r="P17" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E18" s="3">
         <v>1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>700</v>
       </c>
       <c r="J18" s="3">
         <v>700</v>
       </c>
       <c r="K18" s="3">
+        <v>700</v>
+      </c>
+      <c r="L18" s="3">
         <v>2500</v>
-      </c>
-      <c r="L18" s="3">
-        <v>2700</v>
       </c>
       <c r="M18" s="3">
         <v>2700</v>
       </c>
       <c r="N18" s="3">
-        <v>1600</v>
+        <v>2700</v>
       </c>
       <c r="O18" s="3">
         <v>1600</v>
       </c>
       <c r="P18" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q18" s="3">
         <v>1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,8 +1275,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1267,84 +1300,90 @@
         <v>100</v>
       </c>
       <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-1800</v>
       </c>
       <c r="L20" s="3">
         <v>-1800</v>
       </c>
       <c r="M20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E21" s="3">
         <v>1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1369,8 +1408,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1393,81 +1432,87 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
@@ -1476,25 +1521,28 @@
         <v>200</v>
       </c>
       <c r="M24" s="3">
+        <v>200</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>900</v>
+      </c>
+      <c r="E26" s="3">
         <v>700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>400</v>
-      </c>
-      <c r="J26" s="3">
-        <v>600</v>
       </c>
       <c r="K26" s="3">
         <v>600</v>
       </c>
       <c r="L26" s="3">
+        <v>600</v>
+      </c>
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>900</v>
+      </c>
+      <c r="E27" s="3">
         <v>700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>400</v>
-      </c>
-      <c r="J27" s="3">
-        <v>600</v>
       </c>
       <c r="K27" s="3">
         <v>600</v>
       </c>
       <c r="L27" s="3">
+        <v>600</v>
+      </c>
+      <c r="M27" s="3">
         <v>700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,8 +1909,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1867,84 +1936,90 @@
         <v>-100</v>
       </c>
       <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>1800</v>
       </c>
       <c r="L32" s="3">
         <v>1800</v>
       </c>
       <c r="M32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N32" s="3">
         <v>1700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>900</v>
+      </c>
+      <c r="E33" s="3">
         <v>700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>600</v>
       </c>
       <c r="K33" s="3">
         <v>600</v>
       </c>
       <c r="L33" s="3">
+        <v>600</v>
+      </c>
+      <c r="M33" s="3">
         <v>700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>900</v>
+      </c>
+      <c r="E35" s="3">
         <v>700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>600</v>
       </c>
       <c r="K35" s="3">
         <v>600</v>
       </c>
       <c r="L35" s="3">
+        <v>600</v>
+      </c>
+      <c r="M35" s="3">
         <v>700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>40999</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40633</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40543</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,44 +2223,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E41" s="3">
         <v>62500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>21700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>29200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2188,8 +2274,11 @@
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2200,7 +2289,7 @@
         <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -2215,17 +2304,17 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>15000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>16900</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2238,8 +2327,11 @@
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2264,8 +2356,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2288,8 +2380,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2311,12 +2406,12 @@
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2338,35 +2433,38 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="3">
         <v>2400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2500</v>
       </c>
       <c r="H45" s="3">
         <v>2500</v>
       </c>
       <c r="I45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2388,35 +2486,38 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E46" s="3">
         <v>66000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>41000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>33200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2438,35 +2539,38 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>170300</v>
+      </c>
+      <c r="E47" s="3">
         <v>169100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>166600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>171900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>174800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>178900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>181800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>185300</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2488,44 +2592,47 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6100</v>
+        <v>6000</v>
       </c>
       <c r="E48" s="3">
         <v>6100</v>
       </c>
       <c r="F48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="G48" s="3">
         <v>6200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>6100</v>
       </c>
       <c r="J48" s="3">
         <v>6100</v>
       </c>
       <c r="K48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="L48" s="3">
         <v>6200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2538,8 +2645,11 @@
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2550,11 +2660,11 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>1600</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -2562,11 +2672,11 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>1700</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
@@ -2588,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2697,35 +2816,35 @@
         <v>9100</v>
       </c>
       <c r="E52" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F52" s="3">
         <v>9000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>9000</v>
       </c>
       <c r="I52" s="3">
         <v>9000</v>
       </c>
       <c r="J52" s="3">
+        <v>9000</v>
+      </c>
+      <c r="K52" s="3">
         <v>7000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2738,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,44 +2910,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>469000</v>
+      </c>
+      <c r="E54" s="3">
         <v>492100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>460500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>468800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>484300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>464000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>462300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>472000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>485800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>456500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>457200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2838,8 +2963,11 @@
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,43 +3007,44 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>390800</v>
+      </c>
+      <c r="E57" s="3">
         <v>398600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>377200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>384200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>362800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>350800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>359700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>369900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
+      <c r="N57" s="3">
+        <v>200</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
@@ -2928,35 +3058,38 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E58" s="3">
         <v>57000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>49800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>53100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>84000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>72200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2978,13 +3111,16 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>100</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>4</v>
@@ -3004,8 +3140,8 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -3028,35 +3164,38 @@
       <c r="R59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>394500</v>
+      </c>
+      <c r="E60" s="3">
         <v>456300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>427700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>438000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>366600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>436500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>362800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>442600</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3078,44 +3217,47 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>88800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>73600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3128,8 +3270,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3137,26 +3282,26 @@
         <v>3400</v>
       </c>
       <c r="E62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F62" s="3">
         <v>3800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -3178,8 +3323,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,44 +3482,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>439100</v>
+      </c>
+      <c r="E66" s="3">
         <v>461300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>433200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>443200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>459000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>442000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>440000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>449200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>464300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>436100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>435200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3378,8 +3535,11 @@
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,44 +3768,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E72" s="3">
         <v>34200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>33700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>32700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>32300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>32100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>31800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>31500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>31100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>30200</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3648,8 +3821,11 @@
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,44 +3980,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E76" s="3">
         <v>30800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>27300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3848,8 +4033,11 @@
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>40999</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40633</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40543</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>900</v>
+      </c>
+      <c r="E81" s="3">
         <v>700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>600</v>
       </c>
       <c r="K81" s="3">
         <v>600</v>
       </c>
       <c r="L81" s="3">
+        <v>600</v>
+      </c>
+      <c r="M81" s="3">
         <v>700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4049,8 +4247,8 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -4073,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,8 +4536,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4349,8 +4565,8 @@
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -4373,8 +4589,11 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4419,32 +4639,35 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,8 +4769,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4569,8 +4798,8 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -4593,8 +4822,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4639,8 +4872,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4663,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,8 +5055,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4839,8 +5084,8 @@
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -4863,8 +5108,11 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4889,8 +5137,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4913,8 +5161,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4939,8 +5190,8 @@
       <c r="J102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -4961,6 +5212,9 @@
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FRFC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FRFC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="92">
   <si>
     <t>FRFC</t>
   </si>
@@ -656,132 +656,140 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>40633</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>40543</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>4000</v>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3">
         <v>3600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M8" s="3">
         <v>3100</v>
       </c>
-      <c r="I8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O8" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P8" s="3">
         <v>3100</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3700</v>
-      </c>
-      <c r="M8" s="3">
-        <v>3300</v>
-      </c>
-      <c r="N8" s="3">
-        <v>3100</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2100</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2100</v>
       </c>
       <c r="Q8" s="3">
         <v>2100</v>
@@ -790,10 +798,16 @@
         <v>2100</v>
       </c>
       <c r="S8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="U8" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -845,41 +859,47 @@
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>4000</v>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E10" s="3">
-        <v>3800</v>
-      </c>
-      <c r="F10" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G10" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="3">
         <v>3600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M10" s="3">
         <v>3100</v>
       </c>
-      <c r="I10" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>3100</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
@@ -898,8 +918,14 @@
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,8 +945,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -972,8 +1000,14 @@
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,8 +1059,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1054,11 +1094,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1078,40 +1118,46 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1131,8 +1177,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1201,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>2700</v>
+      <c r="D17" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E17" s="3">
         <v>2800</v>
       </c>
-      <c r="F17" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="3">
         <v>2700</v>
       </c>
-      <c r="H17" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>1200</v>
+      <c r="D18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>600</v>
+        <v>1300</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I18" s="3">
         <v>800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
+        <v>800</v>
+      </c>
+      <c r="L18" s="3">
         <v>700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,114 +1342,128 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>1400</v>
       </c>
-      <c r="E21" s="3">
-        <v>1100</v>
-      </c>
       <c r="F21" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <v>900</v>
       </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>900</v>
+      </c>
+      <c r="L21" s="3">
         <v>800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1411,11 +1491,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1435,96 +1515,108 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3">
         <v>1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3">
+        <v>800</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="3">
+        <v>700</v>
+      </c>
+      <c r="L23" s="3">
+        <v>600</v>
+      </c>
+      <c r="M23" s="3">
+        <v>800</v>
+      </c>
+      <c r="N23" s="3">
+        <v>700</v>
+      </c>
+      <c r="O23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="P23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>600</v>
+      </c>
+      <c r="R23" s="3">
+        <v>900</v>
+      </c>
+      <c r="S23" s="3">
+        <v>100</v>
+      </c>
+      <c r="T23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
-        <v>500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>600</v>
-      </c>
-      <c r="K23" s="3">
-        <v>800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>700</v>
-      </c>
-      <c r="M23" s="3">
-        <v>900</v>
-      </c>
-      <c r="N23" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O23" s="3">
-        <v>600</v>
-      </c>
-      <c r="P23" s="3">
-        <v>900</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>100</v>
-      </c>
-      <c r="R23" s="3">
-        <v>800</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
-        <v>200</v>
-      </c>
-      <c r="F24" s="3">
-        <v>400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
-        <v>100</v>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
       </c>
       <c r="L24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>200</v>
       </c>
       <c r="N24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O24" s="3">
         <v>200</v>
@@ -1533,16 +1625,22 @@
         <v>300</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R24" s="3">
         <v>300</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>300</v>
+      </c>
+      <c r="U24" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1692,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3">
         <v>900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="3">
+        <v>600</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="3">
+        <v>500</v>
+      </c>
+      <c r="L26" s="3">
+        <v>400</v>
+      </c>
+      <c r="M26" s="3">
+        <v>600</v>
+      </c>
+      <c r="N26" s="3">
+        <v>600</v>
+      </c>
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="F26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="P26" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>400</v>
+      </c>
+      <c r="R26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
-        <v>400</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="S26" s="3">
+        <v>100</v>
+      </c>
+      <c r="T26" s="3">
         <v>500</v>
       </c>
-      <c r="J26" s="3">
-        <v>400</v>
-      </c>
-      <c r="K26" s="3">
-        <v>600</v>
-      </c>
-      <c r="L26" s="3">
-        <v>600</v>
-      </c>
-      <c r="M26" s="3">
-        <v>700</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="U26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
-        <v>400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
-      <c r="R26" s="3">
-        <v>500</v>
-      </c>
-      <c r="S26" s="3">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3">
         <v>900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" s="3">
+        <v>600</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="3">
+        <v>500</v>
+      </c>
+      <c r="L27" s="3">
+        <v>400</v>
+      </c>
+      <c r="M27" s="3">
+        <v>600</v>
+      </c>
+      <c r="N27" s="3">
+        <v>600</v>
+      </c>
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="P27" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>400</v>
+      </c>
+      <c r="R27" s="3">
         <v>600</v>
       </c>
-      <c r="H27" s="3">
-        <v>400</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="S27" s="3">
+        <v>100</v>
+      </c>
+      <c r="T27" s="3">
         <v>500</v>
       </c>
-      <c r="J27" s="3">
-        <v>400</v>
-      </c>
-      <c r="K27" s="3">
-        <v>600</v>
-      </c>
-      <c r="L27" s="3">
-        <v>600</v>
-      </c>
-      <c r="M27" s="3">
-        <v>700</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="U27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
-        <v>400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
-      <c r="R27" s="3">
-        <v>500</v>
-      </c>
-      <c r="S27" s="3">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1869,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1928,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1987,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +2046,132 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-100</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
         <v>900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I33" s="3">
+        <v>600</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="3">
+        <v>500</v>
+      </c>
+      <c r="L33" s="3">
+        <v>400</v>
+      </c>
+      <c r="M33" s="3">
+        <v>600</v>
+      </c>
+      <c r="N33" s="3">
+        <v>600</v>
+      </c>
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="F33" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="P33" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>400</v>
+      </c>
+      <c r="R33" s="3">
         <v>600</v>
       </c>
-      <c r="H33" s="3">
-        <v>400</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="S33" s="3">
+        <v>100</v>
+      </c>
+      <c r="T33" s="3">
         <v>500</v>
       </c>
-      <c r="J33" s="3">
-        <v>400</v>
-      </c>
-      <c r="K33" s="3">
-        <v>600</v>
-      </c>
-      <c r="L33" s="3">
-        <v>600</v>
-      </c>
-      <c r="M33" s="3">
-        <v>700</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
-        <v>400</v>
-      </c>
-      <c r="P33" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>100</v>
-      </c>
-      <c r="R33" s="3">
-        <v>500</v>
-      </c>
-      <c r="S33" s="3">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2223,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
         <v>900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="3">
+        <v>600</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
+        <v>500</v>
+      </c>
+      <c r="L35" s="3">
+        <v>400</v>
+      </c>
+      <c r="M35" s="3">
+        <v>600</v>
+      </c>
+      <c r="N35" s="3">
+        <v>600</v>
+      </c>
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="F35" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="P35" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>400</v>
+      </c>
+      <c r="R35" s="3">
         <v>600</v>
       </c>
-      <c r="H35" s="3">
-        <v>400</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="S35" s="3">
+        <v>100</v>
+      </c>
+      <c r="T35" s="3">
         <v>500</v>
       </c>
-      <c r="J35" s="3">
-        <v>400</v>
-      </c>
-      <c r="K35" s="3">
-        <v>600</v>
-      </c>
-      <c r="L35" s="3">
-        <v>600</v>
-      </c>
-      <c r="M35" s="3">
-        <v>700</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
-        <v>400</v>
-      </c>
-      <c r="P35" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>100</v>
-      </c>
-      <c r="R35" s="3">
-        <v>500</v>
-      </c>
-      <c r="S35" s="3">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>40633</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>40543</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2373,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,50 +2396,52 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>25700</v>
+      <c r="D41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E41" s="3">
-        <v>62500</v>
-      </c>
-      <c r="F41" s="3">
-        <v>22000</v>
-      </c>
-      <c r="G41" s="3">
+        <v>46000</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3">
         <v>22700</v>
       </c>
-      <c r="H41" s="3">
-        <v>38400</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>21700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>30700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>29200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>18400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2277,19 +2451,25 @@
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -2307,20 +2487,20 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>15000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>4600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>16900</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
@@ -2330,8 +2510,14 @@
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2359,11 +2545,11 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2383,8 +2569,14 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2409,15 +2601,15 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
         <v>100</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
@@ -2436,41 +2628,47 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2200</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E45" s="3">
         <v>2400</v>
       </c>
-      <c r="F45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3">
         <v>2800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>2500</v>
       </c>
-      <c r="I45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -2489,41 +2687,47 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>28000</v>
+      <c r="D46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E46" s="3">
-        <v>66000</v>
-      </c>
-      <c r="F46" s="3">
-        <v>25600</v>
-      </c>
-      <c r="G46" s="3">
+        <v>48800</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3">
         <v>26300</v>
       </c>
-      <c r="H46" s="3">
-        <v>41000</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>24700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>20600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>33200</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -2542,41 +2746,47 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>170300</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E47" s="3">
-        <v>169100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>166600</v>
-      </c>
-      <c r="G47" s="3">
+        <v>153800</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3">
         <v>171900</v>
       </c>
-      <c r="H47" s="3">
-        <v>174800</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>178900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>181800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>185300</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -2595,50 +2805,56 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>6000</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E48" s="3">
-        <v>6100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>6100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>6200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6100</v>
+        <v>5900</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I48" s="3">
         <v>6200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="L48" s="3">
         <v>6100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>6200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2648,41 +2864,47 @@
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3">
         <v>1600</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>1700</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
@@ -2701,8 +2923,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2982,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,50 +3041,56 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>9100</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E52" s="3">
-        <v>9100</v>
-      </c>
-      <c r="F52" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3">
+        <v>7200</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>9000</v>
       </c>
-      <c r="G52" s="3">
-        <v>7200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>8900</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>9000</v>
       </c>
-      <c r="J52" s="3">
-        <v>9000</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>7000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>5600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>5900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>5000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2860,8 +3100,14 @@
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,50 +3159,56 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>469000</v>
+      <c r="D54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E54" s="3">
-        <v>492100</v>
-      </c>
-      <c r="F54" s="3">
-        <v>460500</v>
-      </c>
-      <c r="G54" s="3">
+        <v>477600</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3">
         <v>468800</v>
       </c>
-      <c r="H54" s="3">
-        <v>484300</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>464000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>462300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>472000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>485800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>456500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>457200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2966,8 +3218,14 @@
       <c r="S54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3245,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,50 +3268,52 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>390800</v>
+      <c r="D57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E57" s="3">
-        <v>398600</v>
-      </c>
-      <c r="F57" s="3">
-        <v>377200</v>
-      </c>
-      <c r="G57" s="3">
+        <v>395700</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3">
         <v>384200</v>
       </c>
-      <c r="H57" s="3">
-        <v>362800</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>350800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>359700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>369900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3061,41 +3323,47 @@
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>2900</v>
+      <c r="D58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E58" s="3">
-        <v>57000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>49800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>53100</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2000</v>
+        <v>44200</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I58" s="3">
+        <v>52500</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K58" s="3">
         <v>84000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>72200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3114,17 +3382,23 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3143,11 +3417,11 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -3167,41 +3441,47 @@
       <c r="S59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>394500</v>
+      <c r="D60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E60" s="3">
-        <v>456300</v>
-      </c>
-      <c r="F60" s="3">
-        <v>427700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>438000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>366600</v>
+        <v>440600</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I60" s="3">
+        <v>437400</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>436500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>362800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>442600</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3220,50 +3500,56 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>41200</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="F61" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>1300</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>88800</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>2200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>73600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3273,41 +3559,47 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>3400</v>
       </c>
-      <c r="E62" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>3800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -3326,8 +3618,14 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3677,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3736,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,50 +3795,56 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>439100</v>
+      <c r="D66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E66" s="3">
-        <v>461300</v>
-      </c>
-      <c r="F66" s="3">
-        <v>433200</v>
-      </c>
-      <c r="G66" s="3">
+        <v>445300</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3">
         <v>443200</v>
       </c>
-      <c r="H66" s="3">
-        <v>459000</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>442000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>440000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>449200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>464300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>436100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>435200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3538,8 +3854,14 @@
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3881,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3936,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3995,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +4054,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,50 +4113,56 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>34900</v>
+      <c r="D72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E72" s="3">
-        <v>34200</v>
-      </c>
-      <c r="F72" s="3">
-        <v>33700</v>
-      </c>
-      <c r="G72" s="3">
+        <v>35700</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3">
         <v>32700</v>
       </c>
-      <c r="H72" s="3">
-        <v>32300</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>32100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>31800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>31500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>31100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>30700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>30200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3824,8 +4172,14 @@
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4231,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4290,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,50 +4349,56 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>30000</v>
+      <c r="D76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E76" s="3">
-        <v>30800</v>
-      </c>
-      <c r="F76" s="3">
-        <v>27300</v>
-      </c>
-      <c r="G76" s="3">
+        <v>32300</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3">
         <v>25600</v>
       </c>
-      <c r="H76" s="3">
-        <v>25300</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>22000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>22200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>22800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>21500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>20400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>22000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4036,8 +4408,14 @@
       <c r="S76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4467,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>40633</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>40543</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>40451</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3">
         <v>900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I81" s="3">
+        <v>600</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K81" s="3">
+        <v>500</v>
+      </c>
+      <c r="L81" s="3">
+        <v>400</v>
+      </c>
+      <c r="M81" s="3">
+        <v>600</v>
+      </c>
+      <c r="N81" s="3">
+        <v>600</v>
+      </c>
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="F81" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="P81" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>400</v>
+      </c>
+      <c r="R81" s="3">
         <v>600</v>
       </c>
-      <c r="H81" s="3">
-        <v>400</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="S81" s="3">
+        <v>100</v>
+      </c>
+      <c r="T81" s="3">
         <v>500</v>
       </c>
-      <c r="J81" s="3">
-        <v>400</v>
-      </c>
-      <c r="K81" s="3">
-        <v>600</v>
-      </c>
-      <c r="L81" s="3">
-        <v>600</v>
-      </c>
-      <c r="M81" s="3">
-        <v>700</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
-        <v>400</v>
-      </c>
-      <c r="P81" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>100</v>
-      </c>
-      <c r="R81" s="3">
-        <v>500</v>
-      </c>
-      <c r="S81" s="3">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,8 +4617,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4250,11 +4648,11 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4274,8 +4672,14 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4731,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4790,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4849,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4908,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,8 +4967,14 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4568,11 +5002,11 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -4592,8 +5026,14 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +5053,10 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4642,11 +5084,11 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -4664,10 +5106,16 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +5167,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,8 +5226,14 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4801,11 +5261,11 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -4825,8 +5285,14 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5312,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4875,11 +5343,11 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4899,8 +5367,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5426,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5485,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,8 +5544,14 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5087,11 +5579,11 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -5111,8 +5603,14 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5140,11 +5638,11 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5164,8 +5662,14 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5193,11 +5697,11 @@
       <c r="K102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -5215,6 +5719,12 @@
         <v>0</v>
       </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>
